--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M313"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4366645.5</v>
+        <v>4833.65</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18658073.07</v>
+        <v>20653.53</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>665057.6800000001</v>
+        <v>736.1799999999999</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>562552.27</v>
+        <v>622.72</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>609584.64</v>
+        <v>674.78</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7187588.1</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>634772.1800000001</v>
+        <v>702.66</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>534409.96</v>
+        <v>591.5599999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>528463.53</v>
+        <v>584.98</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>775581.3100000001</v>
+        <v>858.53</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3288954.13</v>
+        <v>3640.7</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>862504.86</v>
+        <v>954.75</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7888.44</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>454938.19</v>
+        <v>503.59</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>923489.98</v>
+        <v>1022.26</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3992088.24</v>
+        <v>4419.04</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>665057.6800000001</v>
+        <v>736.1799999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7888.44</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3691350.25</v>
+        <v>4086.14</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8365.57</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1223560.38</v>
+        <v>1354.42</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8365.57</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1109412.01</v>
+        <v>1228.06</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8365.57</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>592052.37</v>
+        <v>655.37</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>19094823.3</v>
+        <v>21136.99</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1431570</v>
+        <v>1584.67</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8618.26</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>626227.98</v>
+        <v>693.2</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>447648.25</v>
+        <v>495.52</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>871882.0600000001</v>
+        <v>965.13</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1008713.02</v>
+        <v>1116.59</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7198211.23</v>
+        <v>7968.05</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7553872.48</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>291312</v>
+        <v>322.47</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>690027.45</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>10340409.8</v>
+        <v>11446.3</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2887644.48</v>
+        <v>3196.47</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>445683.56</v>
+        <v>493.35</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>373145.92</v>
+        <v>413.05</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1875967.17</v>
+        <v>2076.6</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>632405.27</v>
+        <v>700.04</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>14375176.2</v>
+        <v>15912.58</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>908241.3199999999</v>
+        <v>1005.38</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>901398.8199999999</v>
+        <v>997.8</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>894916.89</v>
+        <v>990.63</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>611826.6</v>
+        <v>677.26</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1812425.93</v>
+        <v>2006.26</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1350283.48</v>
+        <v>1494.69</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8365.57</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7553872.48</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>582237.25</v>
+        <v>644.51</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4604752.6</v>
+        <v>5097.22</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8618.26</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>572581.59</v>
+        <v>633.8200000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7198211.23</v>
+        <v>7968.05</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1236495.68</v>
+        <v>1368.74</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7033316.5</v>
+        <v>7785.52</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5902131.06</v>
+        <v>6533.36</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>371728.63</v>
+        <v>411.48</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7553872.48</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8618.26</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8389500</v>
+        <v>9286.75</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>9986004</v>
+        <v>11053.99</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>12134430</v>
+        <v>13432.19</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>152753.16</v>
+        <v>169.09</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>469928.62</v>
+        <v>520.1900000000001</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1231175.19</v>
+        <v>1362.85</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>610702.05</v>
+        <v>676.02</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2390320.87</v>
+        <v>2645.96</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>461744.99</v>
+        <v>511.13</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>8909744.199999999</v>
+        <v>9862.629999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>460810.84</v>
+        <v>510.09</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>155870.96</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11254517.82</v>
+        <v>12458.17</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>7553872.48</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>967264.13</v>
+        <v>1070.71</v>
       </c>
     </row>
     <row r="87">
@@ -5750,11 +5750,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>631771</v>
+        <v>699.34</v>
       </c>
     </row>
     <row r="88">
@@ -5811,11 +5811,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8618.26</v>
       </c>
     </row>
     <row r="89">
@@ -5872,11 +5872,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8197503.02</v>
+        <v>9074.209999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5933,11 +5933,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="91">
@@ -5994,11 +5994,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>697798.15</v>
+        <v>772.4299999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6055,11 +6055,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>15979967.36</v>
+        <v>17689</v>
       </c>
     </row>
     <row r="93">
@@ -6116,11 +6116,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>250754.42</v>
+        <v>277.57</v>
       </c>
     </row>
     <row r="94">
@@ -6177,11 +6177,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1289683.92</v>
+        <v>1427.61</v>
       </c>
     </row>
     <row r="95">
@@ -6238,11 +6238,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>17455753</v>
+        <v>19322.62</v>
       </c>
     </row>
     <row r="96">
@@ -6299,11 +6299,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7785597.61</v>
+        <v>8618.26</v>
       </c>
     </row>
     <row r="97">
@@ -6360,11 +6360,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7553872.48</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="98">
@@ -6421,11 +6421,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>461744.99</v>
+        <v>511.13</v>
       </c>
     </row>
     <row r="99">
@@ -6482,11 +6482,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7187588.1</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="100">
@@ -6543,11 +6543,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>181414.31</v>
+        <v>200.82</v>
       </c>
     </row>
     <row r="101">
@@ -6604,11 +6604,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>15208249.98</v>
+        <v>16834.75</v>
       </c>
     </row>
     <row r="102">
@@ -6665,11 +6665,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2316383.79</v>
+        <v>2564.12</v>
       </c>
     </row>
     <row r="103">
@@ -6726,11 +6726,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>7604124.99</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6787,11 +6787,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>846863.5</v>
+        <v>937.4299999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6848,11 +6848,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1891695.4</v>
+        <v>2094.01</v>
       </c>
     </row>
     <row r="106">
@@ -6909,11 +6909,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5551588</v>
+        <v>6145.32</v>
       </c>
     </row>
     <row r="107">
@@ -6974,11 +6974,11 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>695066505</v>
+        <v>769402.91</v>
       </c>
     </row>
     <row r="108">
@@ -7035,11 +7035,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2814112</v>
+        <v>3115.08</v>
       </c>
     </row>
     <row r="109">
@@ -7096,11 +7096,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>645099</v>
+        <v>714.09</v>
       </c>
     </row>
     <row r="110">
@@ -7157,11 +7157,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2728908</v>
+        <v>3020.76</v>
       </c>
     </row>
     <row r="111">
@@ -7218,11 +7218,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3489496.5</v>
+        <v>3862.69</v>
       </c>
     </row>
     <row r="112">
@@ -7279,11 +7279,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4775291.5</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="113">
@@ -7340,11 +7340,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5894427</v>
+        <v>6524.83</v>
       </c>
     </row>
     <row r="114">
@@ -7401,11 +7401,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>12489145.2</v>
+        <v>13824.84</v>
       </c>
     </row>
     <row r="115">
@@ -7462,11 +7462,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6988628.43</v>
+        <v>7736.05</v>
       </c>
     </row>
     <row r="116">
@@ -7523,11 +7523,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8018220</v>
+        <v>8875.76</v>
       </c>
     </row>
     <row r="117">
@@ -7584,11 +7584,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1303803.27</v>
+        <v>1443.24</v>
       </c>
     </row>
     <row r="118">
@@ -7645,11 +7645,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4366764.5</v>
+        <v>4833.78</v>
       </c>
     </row>
     <row r="119">
@@ -7706,11 +7706,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="120">
@@ -7767,11 +7767,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>576614.5</v>
+        <v>638.28</v>
       </c>
     </row>
     <row r="121">
@@ -7828,11 +7828,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>16390484.04</v>
+        <v>18143.42</v>
       </c>
     </row>
     <row r="122">
@@ -7889,11 +7889,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="123">
@@ -7950,11 +7950,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2799951</v>
+        <v>3099.4</v>
       </c>
     </row>
     <row r="124">
@@ -8011,11 +8011,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2958887.4</v>
+        <v>3275.34</v>
       </c>
     </row>
     <row r="125">
@@ -8072,11 +8072,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>767601.17</v>
+        <v>849.7</v>
       </c>
     </row>
     <row r="126">
@@ -8133,11 +8133,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>15237683.44</v>
+        <v>16867.33</v>
       </c>
     </row>
     <row r="127">
@@ -8194,11 +8194,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>152748.4</v>
+        <v>169.08</v>
       </c>
     </row>
     <row r="128">
@@ -8255,11 +8255,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>152748.4</v>
+        <v>169.08</v>
       </c>
     </row>
     <row r="129">
@@ -8316,11 +8316,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>423756.62</v>
+        <v>469.08</v>
       </c>
     </row>
     <row r="130">
@@ -8377,11 +8377,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>664961.29</v>
+        <v>736.08</v>
       </c>
     </row>
     <row r="131">
@@ -8438,11 +8438,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="132">
@@ -8499,11 +8499,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>539585.27</v>
+        <v>597.29</v>
       </c>
     </row>
     <row r="133">
@@ -8560,11 +8560,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7888.44</v>
       </c>
     </row>
     <row r="134">
@@ -8621,11 +8621,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>436492</v>
+        <v>483.17</v>
       </c>
     </row>
     <row r="135">
@@ -8682,11 +8682,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7618841.72</v>
+        <v>8433.67</v>
       </c>
     </row>
     <row r="136">
@@ -8743,11 +8743,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>17013227.7</v>
+        <v>18832.77</v>
       </c>
     </row>
     <row r="137">
@@ -8804,11 +8804,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>755250.16</v>
+        <v>836.02</v>
       </c>
     </row>
     <row r="138">
@@ -8865,11 +8865,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7888.44</v>
       </c>
     </row>
     <row r="139">
@@ -8926,11 +8926,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>507431.47</v>
+        <v>561.7</v>
       </c>
     </row>
     <row r="140">
@@ -8987,11 +8987,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>432463.85</v>
+        <v>478.72</v>
       </c>
     </row>
     <row r="141">
@@ -9048,11 +9048,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1216513.2</v>
+        <v>1346.62</v>
       </c>
     </row>
     <row r="142">
@@ -9109,11 +9109,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4421207</v>
+        <v>4894.05</v>
       </c>
     </row>
     <row r="143">
@@ -9170,11 +9170,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4472496</v>
+        <v>4950.82</v>
       </c>
     </row>
     <row r="144">
@@ -9231,11 +9231,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>761491.71</v>
+        <v>842.9299999999999</v>
       </c>
     </row>
     <row r="145">
@@ -9292,11 +9292,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>811697.8100000001</v>
+        <v>898.51</v>
       </c>
     </row>
     <row r="146">
@@ -9353,11 +9353,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>307119.96</v>
+        <v>339.97</v>
       </c>
     </row>
     <row r="147">
@@ -9414,11 +9414,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="148">
@@ -9475,11 +9475,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>462605.36</v>
+        <v>512.08</v>
       </c>
     </row>
     <row r="149">
@@ -9536,11 +9536,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8365.57</v>
       </c>
     </row>
     <row r="150">
@@ -9597,11 +9597,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>403912.18</v>
+        <v>447.11</v>
       </c>
     </row>
     <row r="151">
@@ -9658,11 +9658,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7888.44</v>
       </c>
     </row>
     <row r="152">
@@ -9719,11 +9719,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>760374.3</v>
+        <v>841.7</v>
       </c>
     </row>
     <row r="153">
@@ -9780,11 +9780,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7915436.13</v>
+        <v>8761.98</v>
       </c>
     </row>
     <row r="154">
@@ -9841,17 +9841,17 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7954942.94</v>
+        <v>8805.709999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1078078-1631-CM26</t>
+          <t>1078078-1632-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9891,28 +9891,28 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>7915436.13</v>
+        <v>700.17</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1078078-1632-CM26</t>
+          <t>1078078-1631-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9952,22 +9952,22 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>632525.46</v>
+        <v>8761.98</v>
       </c>
     </row>
     <row r="157">
@@ -10024,17 +10024,17 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>984784.5</v>
+        <v>1090.11</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1078078-1621-CM26</t>
+          <t>1250355-16-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.933.800-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10074,22 +10074,22 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>348472.46</v>
+        <v>20393.89</v>
       </c>
     </row>
     <row r="159">
@@ -10146,11 +10146,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7187588.1</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="160">
@@ -10207,11 +10207,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>299080.32</v>
+        <v>331.07</v>
       </c>
     </row>
     <row r="161">
@@ -10268,17 +10268,17 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>7989983.68</v>
+        <v>8844.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1250355-16-CM26</t>
+          <t>1078078-1621-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.933.800-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10318,22 +10318,22 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>18423520.5</v>
+        <v>385.74</v>
       </c>
     </row>
     <row r="163">
@@ -10390,11 +10390,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>23969951.04</v>
+        <v>26533.5</v>
       </c>
     </row>
     <row r="164">
@@ -10451,11 +10451,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>376128.06</v>
+        <v>416.35</v>
       </c>
     </row>
     <row r="165">
@@ -10512,11 +10512,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>595045.22</v>
+        <v>658.6799999999999</v>
       </c>
     </row>
     <row r="166">
@@ -10573,11 +10573,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7557322.29</v>
+        <v>8365.57</v>
       </c>
     </row>
     <row r="167">
@@ -10634,11 +10634,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>699455.8199999999</v>
+        <v>774.26</v>
       </c>
     </row>
     <row r="168">
@@ -10695,11 +10695,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>15979967.36</v>
+        <v>17689</v>
       </c>
     </row>
     <row r="169">
@@ -10760,11 +10760,11 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>28676992.47</v>
+        <v>31743.96</v>
       </c>
     </row>
     <row r="170">
@@ -10821,11 +10821,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>494683</v>
+        <v>547.59</v>
       </c>
     </row>
     <row r="171">
@@ -10882,11 +10882,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="172">
@@ -10943,11 +10943,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>184886.73</v>
+        <v>204.66</v>
       </c>
     </row>
     <row r="173">
@@ -11004,11 +11004,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>155866.2</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="174">
@@ -11065,17 +11065,17 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1418491.9</v>
+        <v>1570.2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1078078-1652-CM26</t>
+          <t>1078078-1651-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11115,28 +11115,28 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>7604124.99</v>
+        <v>277.57</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1078078-1651-CM26</t>
+          <t>1078078-1649-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -11176,28 +11176,28 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>250752.04</v>
+        <v>833.6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1078078-1649-CM26</t>
+          <t>1078078-1652-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11237,22 +11237,22 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>753060.5600000001</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="178">
@@ -11309,17 +11309,17 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>419928.39</v>
+        <v>464.84</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2817-299-CM26</t>
+          <t>1078078-1646-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11344,43 +11344,43 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>521623.41</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1078078-1646-CM26</t>
+          <t>1078078-1645-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11420,28 +11420,28 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7187588.1</v>
+        <v>38312.02</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1078078-1645-CM26</t>
+          <t>1078078-1644-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11481,28 +11481,28 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>34610474.08</v>
+        <v>24206.79</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1078078-1644-CM26</t>
+          <t>1078078-1643-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11542,28 +11542,28 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>21868033.81</v>
+        <v>355.66</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1078078-1643-CM26</t>
+          <t>758-425-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11583,17 +11583,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11603,28 +11603,28 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>321295.24</v>
+        <v>1557.54</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>758-425-CM26</t>
+          <t>758-424-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11675,17 +11675,17 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1407056</v>
+        <v>6041.52</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>758-424-CM26</t>
+          <t>758-422-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11736,17 +11736,17 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5457816</v>
+        <v>3072.66</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>758-422-CM26</t>
+          <t>2817-299-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11766,42 +11766,42 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2775794</v>
+        <v>577.41</v>
       </c>
     </row>
     <row r="187">
@@ -11858,17 +11858,17 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>7126297.15</v>
+        <v>7888.44</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5349-1183-CM26</t>
+          <t>2291-1079-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11893,43 +11893,43 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1422902.04</v>
+        <v>3496.26</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3047-297-CM26</t>
+          <t>5349-1183-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11954,43 +11954,43 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5446749</v>
+        <v>1575.08</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3506-436-CM26</t>
+          <t>3047-297-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12010,48 +12010,48 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Academia Politécnica Naval</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>9599016</v>
+        <v>6029.27</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2291-1079-CM26</t>
+          <t>3506-436-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12071,42 +12071,42 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3158468.25</v>
+        <v>10625.62</v>
       </c>
     </row>
     <row r="192">
@@ -12163,11 +12163,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1904000</v>
+        <v>2107.63</v>
       </c>
     </row>
     <row r="193">
@@ -12224,11 +12224,11 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>14080965.36</v>
+        <v>15586.91</v>
       </c>
     </row>
     <row r="194">
@@ -12285,17 +12285,17 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>38562735.4</v>
+        <v>42686.97</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2436-694-CM26</t>
+          <t>1285502-18-SE26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12320,43 +12320,47 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>33823346.2</v>
+        <v>3228.87</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1285502-18-SE26</t>
+          <t>2279-341-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12376,52 +12380,48 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.721.492-6</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2916906.58</v>
+        <v>38972.72</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2279-341-CM26</t>
+          <t>2436-694-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12441,48 +12441,48 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>35207340</v>
+        <v>37440.71</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2322-382-CM26</t>
+          <t>1078078-1665-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12502,42 +12502,42 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>4167046.8</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="199">
@@ -12594,11 +12594,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>7187588.1</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="200">
@@ -12655,11 +12655,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1106575.05</v>
+        <v>1224.92</v>
       </c>
     </row>
     <row r="201">
@@ -12716,11 +12716,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="202">
@@ -12777,17 +12777,17 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>962602.9</v>
+        <v>1065.55</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1078078-1666-CM26</t>
+          <t>1078078-1667-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12827,28 +12827,28 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>574145.25</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1078078-1665-CM26</t>
+          <t>1078078-1666-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>7604124.99</v>
+        <v>635.55</v>
       </c>
     </row>
     <row r="205">
@@ -12960,17 +12960,17 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1152347.21</v>
+        <v>1275.59</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1078078-1667-CM26</t>
+          <t>2322-382-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12990,42 +12990,42 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7557254.46</v>
+        <v>4612.71</v>
       </c>
     </row>
     <row r="207">
@@ -13082,11 +13082,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>723187.99</v>
+        <v>800.53</v>
       </c>
     </row>
     <row r="208">
@@ -13143,11 +13143,11 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>8204186.06</v>
+        <v>9081.610000000001</v>
       </c>
     </row>
     <row r="209">
@@ -13204,11 +13204,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>784362.3199999999</v>
+        <v>868.25</v>
       </c>
     </row>
     <row r="210">
@@ -13265,11 +13265,11 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8204186.06</v>
+        <v>9081.610000000001</v>
       </c>
     </row>
     <row r="211">
@@ -13326,11 +13326,11 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8204186.06</v>
+        <v>9081.610000000001</v>
       </c>
     </row>
     <row r="212">
@@ -13387,11 +13387,11 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>918275.4</v>
+        <v>1016.48</v>
       </c>
     </row>
     <row r="213">
@@ -13448,17 +13448,17 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>7553872.48</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1078078-1679-CM26</t>
+          <t>1078078-1684-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>151050.27</v>
+        <v>7968.05</v>
       </c>
     </row>
     <row r="215">
@@ -13570,17 +13570,17 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>155866.2</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1078078-1684-CM26</t>
+          <t>2724-465-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13605,43 +13605,43 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7198211.23</v>
+        <v>7934.05</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2724-465-CM26</t>
+          <t>1078078-1682-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13666,43 +13666,43 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>7167499.71</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1078078-1682-CM26</t>
+          <t>1078078-1681-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13742,28 +13742,28 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>155870.96</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1078078-1681-CM26</t>
+          <t>1078078-1680-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13803,28 +13803,28 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7187588.1</v>
+        <v>333.35</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1078078-1680-CM26</t>
+          <t>1078078-1679-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13875,17 +13875,17 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>301142.59</v>
+        <v>167.2</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1078078-1678-CM26</t>
+          <t>1078078-1677-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13925,28 +13925,28 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>508883.27</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>527481-61-CM26</t>
+          <t>1078078-1678-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13971,43 +13971,43 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>12496088.85</v>
+        <v>563.3099999999999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1078078-1676-CM26</t>
+          <t>1078078-1675-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14047,28 +14047,28 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>7989983.68</v>
+        <v>262.08</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1078078-1675-CM26</t>
+          <t>1078078-1674-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14119,17 +14119,17 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>236761.21</v>
+        <v>248.99</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1078078-1674-CM26</t>
+          <t>1078078-1673-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14180,17 +14180,17 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>224933.8</v>
+        <v>1109.5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1078078-1673-CM26</t>
+          <t>1078078-1672-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14241,17 +14241,17 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1002308.44</v>
+        <v>898.13</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1078078-1672-CM26</t>
+          <t>898-2056-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14271,48 +14271,48 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>811353.9</v>
+        <v>265.22</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>898-2056-CM26</t>
+          <t>527481-61-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14332,42 +14332,42 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>239594.6</v>
+        <v>13832.53</v>
       </c>
     </row>
     <row r="229">
@@ -14424,17 +14424,17 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1154776</v>
+        <v>1278.28</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1078078-1677-CM26</t>
+          <t>1078078-1676-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14474,28 +14474,28 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8844.5</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1078078-1695-CM26</t>
+          <t>3596-479-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14520,43 +14520,43 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>139127.66</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1078078-1696-CM26</t>
+          <t>1078078-1695-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14596,28 +14596,28 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>7553872.48</v>
+        <v>154.01</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1078078-1697-CM26</t>
+          <t>1078078-1696-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14657,28 +14657,28 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>157207.33</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1078078-1687-CM26</t>
+          <t>1078078-1701-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14718,22 +14718,22 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1098336.68</v>
+        <v>17689</v>
       </c>
     </row>
     <row r="235">
@@ -14790,11 +14790,11 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>15979967.36</v>
+        <v>17689</v>
       </c>
     </row>
     <row r="236">
@@ -14851,17 +14851,17 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>250752.04</v>
+        <v>277.57</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1078078-1701-CM26</t>
+          <t>1078078-1694-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14901,28 +14901,28 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>15979967.36</v>
+        <v>369.24</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3596-479-CM26</t>
+          <t>1078078-1698-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14947,43 +14947,43 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2866353</v>
+        <v>2260.09</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1078078-1698-CM26</t>
+          <t>1078078-1693-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15023,28 +15023,28 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2041731.79</v>
+        <v>7956.29</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078078-1694-CM26</t>
+          <t>1078078-1686-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15084,28 +15084,28 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>333568.9</v>
+        <v>8761.98</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2069-5561-CM26</t>
+          <t>1078078-1691-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15125,17 +15125,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15145,28 +15145,28 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>7333970</v>
+        <v>8761.98</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1078078-1692-CM26</t>
+          <t>1078078-1690-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15206,28 +15206,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>988243.83</v>
+        <v>3097.45</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078078-1691-CM26</t>
+          <t>1078078-1689-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15278,17 +15278,17 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>7915436.13</v>
+        <v>591.5599999999999</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078078-1690-CM26</t>
+          <t>1078078-1688-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15328,28 +15328,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2798192.18</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1078078-1689-CM26</t>
+          <t>1078078-1687-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15389,28 +15389,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>534408.77</v>
+        <v>1215.8</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1078078-1688-CM26</t>
+          <t>1078078-1692-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15450,28 +15450,28 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7737028.95</v>
+        <v>1093.94</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1078078-1686-CM26</t>
+          <t>1078078-1685-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15511,28 +15511,28 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>7915436.13</v>
+        <v>336.13</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1078078-1685-CM26</t>
+          <t>2069-5561-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15552,17 +15552,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15572,28 +15572,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>303651.11</v>
+        <v>8118.33</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1078078-1693-CM26</t>
+          <t>1285502-19-SE26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15618,43 +15618,47 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr"/>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>7187588.1</v>
+        <v>3228.87</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1285502-19-SE26</t>
+          <t>2483-392-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15669,7 +15673,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -15679,47 +15683,43 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2916906.58</v>
+        <v>26225.77</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2483-392-CM26</t>
+          <t>2788-578-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15734,22 +15734,22 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15759,28 +15759,28 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>23691948</v>
+        <v>1448.47</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2412-385-CM26</t>
+          <t>758-450-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15805,12 +15805,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15820,28 +15820,28 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2343176.64</v>
+        <v>2405.46</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>758-450-CM26</t>
+          <t>1078078-1707-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15861,17 +15861,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15881,28 +15881,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2173053.05</v>
+        <v>7684.76</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1078078-1707-CM26</t>
+          <t>1078078-1706-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15942,28 +15942,28 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>6942294.59</v>
+        <v>1448.19</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1078078-1706-CM26</t>
+          <t>2412-385-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15983,17 +15983,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16003,28 +16003,28 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1308275.29</v>
+        <v>2593.78</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2788-578-CM26</t>
+          <t>1078078-1704-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16044,17 +16044,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16064,28 +16064,28 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1308524</v>
+        <v>504.56</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1078078-1704-CM26</t>
+          <t>1078078-1703-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16125,28 +16125,28 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>455811.65</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1078078-1703-CM26</t>
+          <t>1078078-1702-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16186,28 +16186,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>7553872.48</v>
+        <v>1002.86</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1078078-1702-CM26</t>
+          <t>1159-148-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16232,43 +16232,43 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>905966.04</v>
+        <v>1434.61</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1159-148-CM26</t>
+          <t>1078078-1705-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16288,48 +16288,48 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1296005.2</v>
+        <v>502.25</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1078078-1705-CM26</t>
+          <t>2295-92-SE26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16344,53 +16344,57 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>453723.2</v>
+        <v>47105.53</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2295-92-SE26</t>
+          <t>1078078-1713-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16415,47 +16419,43 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.287.511-k</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>42554400</v>
+        <v>6776.79</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1078078-1713-CM26</t>
+          <t>5349-1254-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16475,48 +16475,48 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>6122050.2</v>
+        <v>1312.57</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1078078-1712-CM26</t>
+          <t>1078078-1710-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -16556,28 +16556,28 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>500527.09</v>
+        <v>680.25</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5349-1254-CM26</t>
+          <t>1078078-1711-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16597,48 +16597,48 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1185751.7</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1078078-1711-CM26</t>
+          <t>3477-446-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16663,43 +16663,43 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>7553872.48</v>
+        <v>34315.41</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1078078-1708-CM26</t>
+          <t>2674-545-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16719,17 +16719,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16739,28 +16739,28 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>455811.65</v>
+        <v>37581.68</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3477-446-CM26</t>
+          <t>1057461-870-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16780,48 +16780,48 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>30999999.8</v>
+        <v>259.8</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2674-545-CM26</t>
+          <t>1078078-1708-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16841,17 +16841,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16861,28 +16861,28 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>33950700</v>
+        <v>504.56</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1057461-870-CM26</t>
+          <t>1078078-1723-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16897,53 +16897,53 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>234703.7</v>
+        <v>469.08</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1078078-1710-CM26</t>
+          <t>1078078-1729-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -16983,28 +16983,28 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>614526.71</v>
+        <v>469.08</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1078078-1723-CM26</t>
+          <t>1078078-1728-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17044,28 +17044,28 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>423756.62</v>
+        <v>450.01</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1078078-1729-CM26</t>
+          <t>1078078-1727-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17105,28 +17105,28 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>423756.62</v>
+        <v>5196.77</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1078078-1728-CM26</t>
+          <t>1078078-1726-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17166,28 +17166,28 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>406527.8</v>
+        <v>8385.52</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1078078-1730-CM26</t>
+          <t>1078078-1725-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17227,28 +17227,28 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1910055.91</v>
+        <v>1619.6</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1078078-1727-CM26</t>
+          <t>1078078-1724-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17288,28 +17288,28 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>4694678.52</v>
+        <v>17128.99</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1078078-1726-CM26</t>
+          <t>1078078-1730-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17349,28 +17349,28 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>7575344.84</v>
+        <v>2114.33</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1078078-1725-CM26</t>
+          <t>1078078-1722-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17410,28 +17410,28 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1463125.23</v>
+        <v>676.01</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1078078-1724-CM26</t>
+          <t>1078078-1720-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17471,28 +17471,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>15474057.9</v>
+        <v>2809.32</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1078078-1722-CM26</t>
+          <t>1078078-1721-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17543,17 +17543,17 @@
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>610700.86</v>
+        <v>7967.21</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1078078-1716-CM26</t>
+          <t>1078078-1719-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17604,17 +17604,17 @@
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>207452.7</v>
+        <v>1559.38</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1078078-1721-CM26</t>
+          <t>1078078-1718-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17665,17 +17665,17 @@
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>7197449.63</v>
+        <v>7967.21</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1078078-1720-CM26</t>
+          <t>1078078-1717-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17715,28 +17715,28 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2537891.58</v>
+        <v>530.24</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1078078-1719-CM26</t>
+          <t>1078078-1716-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17787,17 +17787,17 @@
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1408720.81</v>
+        <v>229.64</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1078078-1718-CM26</t>
+          <t>1078078-1715-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17837,28 +17837,28 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>7197449.63</v>
+        <v>5004.03</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1078078-1717-CM26</t>
+          <t>1078078-1709-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17898,28 +17898,28 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>479008.32</v>
+        <v>7967.21</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1078078-1715-CM26</t>
+          <t>758-456-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17939,17 +17939,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17959,28 +17959,28 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4520558.91</v>
+        <v>3788.9</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1078078-1709-CM26</t>
+          <t>1078078-1741-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -18020,28 +18020,28 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>7197449.63</v>
+        <v>503.53</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>758-456-CM26</t>
+          <t>1078078-1739-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18056,22 +18056,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18081,28 +18081,28 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3422832.7</v>
+        <v>612.92</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1078078-1741-CM26</t>
+          <t>1078078-1738-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18142,28 +18142,28 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>454877.5</v>
+        <v>8433.67</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1078078-1740-CM26</t>
+          <t>1078078-1737-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18203,28 +18203,28 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>7553872.48</v>
+        <v>169.09</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1078078-1739-CM26</t>
+          <t>1078078-1740-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18264,28 +18264,28 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>553705.8100000001</v>
+        <v>8361.75</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1078078-1738-CM26</t>
+          <t>1078078-1735-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18325,28 +18325,28 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>7618841.72</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1078078-1737-CM26</t>
+          <t>1078078-1734-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18386,28 +18386,28 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>76.287.511-k</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>152753.16</v>
+        <v>666</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1078078-1735-CM26</t>
+          <t>1078078-1733-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18447,28 +18447,28 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>7737028.95</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1078078-1734-CM26</t>
+          <t>1078078-1736-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18508,28 +18508,28 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>601658.05</v>
+        <v>1266.8</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1078078-1733-CM26</t>
+          <t>1057486-326-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18544,22 +18544,22 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.608.400-3</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18569,28 +18569,28 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>7604124.99</v>
+        <v>9839.049999999999</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1078078-1736-CM26</t>
+          <t>1078078-1731-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18605,12 +18605,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -18630,28 +18630,28 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1144406.34</v>
+        <v>8417.379999999999</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1057486-326-CM26</t>
+          <t>1078078-1732-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18671,17 +18671,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.608.400-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18691,28 +18691,28 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>8888443.199999999</v>
+        <v>833.8099999999999</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1078078-1731-CM26</t>
+          <t>4494-423-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18732,48 +18732,48 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>7604124.99</v>
+        <v>5372.67</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1078078-1732-CM26</t>
+          <t>2676-389-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18798,12 +18798,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18813,28 +18813,28 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>753253.34</v>
+        <v>2904.38</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>4494-423-CM26</t>
+          <t>1078078-1748-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -18859,43 +18859,43 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4853582.79</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2676-389-CM26</t>
+          <t>1078078-1747-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -18920,12 +18920,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18935,22 +18935,22 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2623771.5</v>
+        <v>8564.49</v>
       </c>
     </row>
     <row r="304">
@@ -19007,17 +19007,17 @@
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>567038.5699999999</v>
+        <v>627.6799999999999</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1078078-1748-CM26</t>
+          <t>1078078-1744-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19068,17 +19068,17 @@
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1078078-1747-CM26</t>
+          <t>2273-381-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19103,12 +19103,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19118,28 +19118,28 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>7737028.95</v>
+        <v>11065.63</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1078078-1744-CM26</t>
+          <t>1078078-1742-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19179,28 +19179,28 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>7557254.46</v>
+        <v>8433.67</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1078078-1749-CM26</t>
+          <t>3340-175-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19220,48 +19220,48 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>732485.46</v>
+        <v>23267.37</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1078078-1742-CM26</t>
+          <t>1078078-1749-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19301,28 +19301,28 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>7618841.72</v>
+        <v>810.8200000000001</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>3340-175-CM26</t>
+          <t>1078078-1743-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19342,48 +19342,48 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>21019374.6</v>
+        <v>1031.08</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2273-381-CM26</t>
+          <t>1078078-1750-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19408,12 +19408,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19423,144 +19423,22 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>9996518.84</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>1078078-1743-CM26</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>ABATTE OFFICITY</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>96.909.950-0</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M312" s="2" t="n">
-        <v>931459.41</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>1078078-1750-CM26</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M313" s="2" t="n">
-        <v>578682.72</v>
+        <v>640.5700000000001</v>
       </c>
     </row>
   </sheetData>
